--- a/foundational_documents/former/DOT_signal_overview.xlsx
+++ b/foundational_documents/former/DOT_signal_overview.xlsx
@@ -47,7 +47,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -84,6 +84,11 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8DAEF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -111,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -135,6 +140,8 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -500,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3289,6 +3296,135 @@
       </c>
       <c r="M59" s="4" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE-VARIABLE (S.20) — conviction sizing + gap entries</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="n"/>
+      <c r="C61" s="15" t="n"/>
+      <c r="D61" s="15" t="n"/>
+      <c r="E61" s="15" t="n"/>
+      <c r="F61" s="15" t="n"/>
+      <c r="G61" s="15" t="n"/>
+      <c r="H61" s="15" t="n"/>
+      <c r="I61" s="15" t="n"/>
+      <c r="J61" s="15" t="n"/>
+      <c r="K61" s="15" t="n"/>
+      <c r="L61" s="15" t="n"/>
+      <c r="M61" s="15" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>SV_Hurst_L</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>6090.6</v>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>19/20</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>-118</v>
+      </c>
+      <c r="M62" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>SV_FailBrk_L</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G63" s="7" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>19834.1</v>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>22/22</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="M63" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3312,7 +3448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5787,6 +5923,108 @@
       <c r="F83" s="4" t="inlineStr">
         <is>
           <t>discrete state/side == value</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>S.20 CONVICTION / GAP THRESHOLDS</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="n"/>
+      <c r="C85" s="15" t="n"/>
+      <c r="D85" s="15" t="n"/>
+      <c r="E85" s="15" t="n"/>
+      <c r="F85" s="15" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Micro_Hurst</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>p90</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>ADAPTIVE (rolling-2500)</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>conviction SIZING gate: book longs &gt; p90 -&gt; 2.0 lots (longs only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Micro_Hurst</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>p97</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>ADAPTIVE (rolling-2500)</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Hurst GAP-single: &gt; p97 &amp; D2D+ -&gt; LONG 1 lot LOCK=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Micro_FailedBreak</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>p90</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>ADAPTIVE (rolling-2500)</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>FailedBreak GAP-single: &gt; p90 &amp; D2D- (reversion) -&gt; LONG 1 lot LOCK=3; recentFB sizing x1.25</t>
         </is>
       </c>
     </row>
@@ -5805,7 +6043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6145,6 +6383,39 @@
       <c r="I9" s="6" t="n">
         <v>0.009430715219935293</v>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>SINGLE-VARIABLE (S.20)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Lone-variable conviction: Micro_Hurst trend-persistence + Micro_FailedBreak reversion — sizes book longs and fills gaps (addendum to the 8 structures)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>467</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>25925</v>
+      </c>
+      <c r="I10" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
